--- a/MAS_Survey.xlsx
+++ b/MAS_Survey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A77FD05F-786A-4BB5-8428-153856858FD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29CB29F7-5AD2-43EA-A500-D692E57FB943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="170" windowWidth="29600" windowHeight="13110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="830" yWindow="510" windowWidth="32880" windowHeight="13040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categorical_Summary" sheetId="2" r:id="rId1"/>
@@ -148,7 +148,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -187,10 +187,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -510,26 +513,26 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.1796875" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16.08984375" customWidth="1"/>
+    <col min="5" max="5" width="9.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -951,4 +954,321 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
+    <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <xsd:import namespace="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:Status" minOccurs="0"/>
+                <xsd:element ref="ns2:Notes" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c3d3890c-cedb-4996-8d69-32a58562dce0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="39ef60d6-d330-4097-af7f-3d123b2b8fd1" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Status" ma:index="22" nillable="true" ma:displayName="Status" ma:format="Dropdown" ma:internalName="Status">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Notes" ma:index="23" nillable="true" ma:displayName="Notes" ma:format="Dropdown" ma:internalName="Notes">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081083fe-e475-436e-8ac6-57ab24d1081c" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a3a1a50f-7a17-49b9-80c3-11c81385b63c}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="081083fe-e475-436e-8ac6-57ab24d1081c">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithUsers" ma:index="20" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="21" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C562A73-D195-48C5-B024-CEBDF0212ECE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA3F8DF1-BCA5-4971-BFCC-7833F584D9AC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10C8DAF9-09C6-4622-B6CD-FD8E8B75085E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>